--- a/outputs/01_问题1/表4_预测结果.xlsx
+++ b/outputs/01_问题1/表4_预测结果.xlsx
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3428568180057713</v>
+        <v>0.3428568180057762</v>
       </c>
     </row>
     <row r="3">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.4050184264836337</v>
+        <v>0.4050184264836325</v>
       </c>
     </row>
     <row r="4">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.3672365750813858</v>
+        <v>0.3672365750813857</v>
       </c>
     </row>
     <row r="5">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.3908744619419623</v>
+        <v>0.3908744619419667</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.3804302351793398</v>
+        <v>0.3804302351793413</v>
       </c>
     </row>
     <row r="7">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.3481521881855416</v>
+        <v>0.3481521881855461</v>
       </c>
     </row>
     <row r="8">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.355375510051415</v>
+        <v>0.3553755100514184</v>
       </c>
     </row>
     <row r="9">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.3583050453791501</v>
+        <v>0.3583050453791531</v>
       </c>
     </row>
     <row r="10">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.3590136660761439</v>
+        <v>0.3590136660761473</v>
       </c>
     </row>
     <row r="11">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.3673187032614716</v>
+        <v>0.3673187032614803</v>
       </c>
     </row>
     <row r="12">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.3656977121079799</v>
+        <v>0.3656977121079895</v>
       </c>
     </row>
     <row r="13">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.3654323937825498</v>
+        <v>0.3654323937825599</v>
       </c>
     </row>
     <row r="14">
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.6425769166551657</v>
+        <v>0.6425769166551825</v>
       </c>
     </row>
     <row r="15">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.6395660105741221</v>
+        <v>0.6395660105741395</v>
       </c>
     </row>
     <row r="16">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.7453726058473742</v>
+        <v>0.7453726058473999</v>
       </c>
     </row>
     <row r="17">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.7792013355451016</v>
+        <v>0.7792013355451249</v>
       </c>
     </row>
     <row r="18">
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.7020367156195009</v>
+        <v>0.7020367156195151</v>
       </c>
     </row>
     <row r="19">
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.7131636652670622</v>
+        <v>0.7131636652670754</v>
       </c>
     </row>
     <row r="20">
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.7004937336261516</v>
+        <v>0.7004937336261624</v>
       </c>
     </row>
     <row r="21">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.6792450586939682</v>
+        <v>0.6792450586939811</v>
       </c>
     </row>
     <row r="22">
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.6667355923519093</v>
+        <v>0.6667355923519197</v>
       </c>
     </row>
     <row r="23">
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.6825598306359836</v>
+        <v>0.6825598306360008</v>
       </c>
     </row>
     <row r="24">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.6992416127292652</v>
+        <v>0.6992416127292802</v>
       </c>
     </row>
     <row r="25">
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.7027211088249519</v>
+        <v>0.7027211088249681</v>
       </c>
     </row>
     <row r="26">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.9386534343833595</v>
+        <v>0.9386534343833997</v>
       </c>
     </row>
     <row r="27">
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.9434534359157708</v>
+        <v>0.9434534359158114</v>
       </c>
     </row>
     <row r="28">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.7752665478979137</v>
+        <v>0.7752665478979135</v>
       </c>
     </row>
     <row r="29">
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.9873120592941619</v>
+        <v>0.9873120592941964</v>
       </c>
     </row>
     <row r="30">
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.080154070346902</v>
+        <v>1.080154070346928</v>
       </c>
     </row>
     <row r="31">
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1.044793177571802</v>
+        <v>1.04479317757183</v>
       </c>
     </row>
     <row r="32">
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1.045483009805055</v>
+        <v>1.045483009805085</v>
       </c>
     </row>
     <row r="33">
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.9895665986204331</v>
+        <v>0.9895665986204665</v>
       </c>
     </row>
     <row r="34">
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.9748404071356045</v>
+        <v>0.9748404071356369</v>
       </c>
     </row>
     <row r="35">
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.9952799685885183</v>
+        <v>0.9952799685885581</v>
       </c>
     </row>
     <row r="36">
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.98887661300275</v>
+        <v>0.9888766130027883</v>
       </c>
     </row>
     <row r="37">
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1.036598547806722</v>
+        <v>1.036598547806763</v>
       </c>
     </row>
   </sheetData>
